--- a/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 14,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,36</t>
+          <t>0,57; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,85</t>
+          <t>0,16; 1,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,15</t>
+          <t>0,38; 2,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,32</t>
+          <t>0,16; 1,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,47</t>
+          <t>1,07; 7,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,22</t>
+          <t>0,71; 4,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,01; 1,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,35; 1,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,08; 0,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,59</t>
+          <t>0,49; 1,76</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4196</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3417</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3972</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3781</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1648</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1267; 7699</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5057</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>424; 5007</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2856</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5071</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5991</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2803</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1747; 9206</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>942; 8127</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1074; 7421</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2978</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3022</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5234</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3477</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4210</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1671; 9808</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1127; 7336</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4644</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10494</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18; 6120</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8558</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5225</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2505; 10386</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>619; 6144</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4279; 15396</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,11</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,49</t>
+          <t>0,51; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,91</t>
+          <t>0,16; 1,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,0</t>
+          <t>0,44; 2,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,12; 1,47</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,42</t>
+          <t>1,17; 7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,16</t>
+          <t>0,75; 3,75</t>
         </is>
       </c>
     </row>
@@ -1142,32 +1142,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,67</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,44</t>
+          <t>0,35; 1,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,84</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,76</t>
+          <t>0,47; 1,73</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3417</t>
+          <t>0; 3090</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3972</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3781</t>
+          <t>0; 3511</t>
         </is>
       </c>
     </row>
@@ -1717,27 +1717,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1267; 7699</t>
+          <t>1129; 7384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5057</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>424; 5007</t>
+          <t>423; 4794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>0; 3165</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5071</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5991</t>
+          <t>0; 6559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2803</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1747; 9206</t>
+          <t>2014; 9653</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 5280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>942; 8127</t>
+          <t>685; 8570</t>
         </is>
       </c>
     </row>
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1074; 7421</t>
+          <t>1170; 7816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2978</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3022</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 4744</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3477</t>
+          <t>0; 3516</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4210</t>
+          <t>0; 3718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1671; 9808</t>
+          <t>1767; 8850</t>
         </is>
       </c>
     </row>
@@ -2133,57 +2133,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1127; 7336</t>
+          <t>1128; 7279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2657; 10494</t>
+          <t>2765; 11093</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18; 6120</t>
+          <t>622; 6206</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 8558</t>
+          <t>0; 8563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2505; 10386</t>
+          <t>2520; 10312</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>619; 6144</t>
+          <t>612; 5975</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4279; 15396</t>
+          <t>4082; 15143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -659,14 +659,14 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -679,24 +679,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,35</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,83</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,58; 3,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,14; 1,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,09</t>
+          <t>0,44; 2,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,47</t>
+          <t>0,11; 0,99</t>
         </is>
       </c>
     </row>
@@ -929,34 +929,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,81</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>1,11; 7,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,75</t>
+          <t>0,71; 4,19</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,43</t>
+          <t>0,34; 1,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,73</t>
+          <t>0,42; 1,46</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3591</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 3540</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 4079</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,49 +1644,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4711</t>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2160</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2650</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1129; 7384</t>
+          <t>0; 4655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423; 4794</t>
+          <t>0; 3445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>1272; 7409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6559</t>
+          <t>367; 4533</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 2874</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2014; 9653</t>
+          <t>2042; 9927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5280</t>
+          <t>0; 4739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>685; 8570</t>
+          <t>656; 5723</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1799,27 +1799,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1867,39 +1867,39 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>695</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4331</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3156</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1170; 7816</t>
+          <t>0; 5587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4744</t>
+          <t>1150; 7605</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 3500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3718</t>
+          <t>0; 4099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1767; 8850</t>
+          <t>1635; 9668</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,49 +2060,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>5452</t>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1128; 7279</t>
+          <t>616; 6517</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2765; 11093</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>622; 6206</t>
+          <t>1142; 7087</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 8563</t>
+          <t>2789; 10451</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2520; 10312</t>
+          <t>2413; 9915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>612; 5975</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4082; 15143</t>
+          <t>3587; 12528</t>
         </is>
       </c>
     </row>
